--- a/Docs/Dev/Moica - Diccionario de Datos.xlsx
+++ b/Docs/Dev/Moica - Diccionario de Datos.xlsx
@@ -8178,7 +8178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -8265,9 +8265,8 @@
           <t>Restricciones BD</t>
         </is>
       </c>
-      <c r="E5" s="8">
-        <f>COUNTA(B24:B24)</f>
-        <v/>
+      <c r="E5" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="G5" s="84" t="inlineStr">
         <is>
@@ -8536,7 +8535,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Aplicación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -8880,6 +8879,51 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>ckCambioEstadoSolicitudTransicion</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>estadoAnterior, estadoNuevo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>estadoNuevo &lt;&gt; estadoAnterior; el registro inicial admite estadoAnterior nulo.</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="E4:F4"/>
@@ -9748,7 +9792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -9835,9 +9879,8 @@
           <t>Restricciones BD</t>
         </is>
       </c>
-      <c r="E5" s="8">
-        <f>COUNTA(B26:B29)</f>
-        <v/>
+      <c r="E5" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="G5" s="84" t="inlineStr">
         <is>
@@ -10106,7 +10149,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Aplicación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -10567,27 +10610,27 @@
       </c>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>uqCalificacionUsuarioSolicitudCalificado</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>idSolicitudServicio, idCalificado</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Cada participante recibe como máximo una calificación por solicitud.</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Base de datos</t>
         </is>
@@ -10601,25 +10644,67 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
+          <t>ckCalificacionUsuarioParticipantes</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>idCalificador, idCalificado</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>idCalificador &lt;&gt; idCalificado.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
           <t>ckCalificacionUsuarioPuntuacion</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>puntuacion</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>puntuacion BETWEEN 1 AND 5.</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Base de datos</t>
         </is>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="E4:F4"/>

--- a/Docs/Dev/Moica - Diccionario de Datos.xlsx
+++ b/Docs/Dev/Moica - Diccionario de Datos.xlsx
@@ -8178,7 +8178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -8265,8 +8265,9 @@
           <t>Restricciones BD</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>2</v>
+      <c r="E5" s="8">
+        <f>COUNTA(B24:B25)</f>
+        <v/>
       </c>
       <c r="G5" s="84" t="inlineStr">
         <is>
@@ -8906,24 +8907,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="E4:F4"/>
@@ -9792,7 +9775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -9879,8 +9862,9 @@
           <t>Restricciones BD</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>5</v>
+      <c r="E5" s="8">
+        <f>COUNTA(B26:B30)</f>
+        <v/>
       </c>
       <c r="G5" s="84" t="inlineStr">
         <is>
@@ -10690,21 +10674,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="E4:F4"/>

--- a/Docs/Dev/Moica - Diccionario de Datos.xlsx
+++ b/Docs/Dev/Moica - Diccionario de Datos.xlsx
@@ -1,35 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisiones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dominios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuario" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Administrador" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SegundoFactorUsuario" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sesion" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departamento" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Municipio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PerfilPrestador" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MedioContactoPrestador" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TrabajoPortafolio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ImagenTrabajoPortafolio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CategoriaServicio" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SubcategoriaServicio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ServicioPublicado" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ImagenServicioPublicado" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SolicitudServicio" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CambioEstadoSolicitud" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MensajeSolicitud" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CalificacionUsuario" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CasoModeracion" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MedidaAdministrativa" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HistorialCaso" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Decisiones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dominios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Usuario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Administrador" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SegundoFactorUsuario" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sesion" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Departamento" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Municipio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PerfilPrestador" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="MedioContactoPrestador" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TrabajoPortafolio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ImagenTrabajoPortafolio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="SolicitudVerificacionPrestador" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="DocumentoVerificacionPrestador" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="CategoriaServicio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SubcategoriaServicio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ServicioPublicado" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="ImagenServicioPublicado" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SolicitudServicio" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="CambioEstadoSolicitud" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="MensajeSolicitud" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="CalificacionUsuario" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="CasoModeracion" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="MedidaAdministrativa" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="HistorialCaso" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1106,7 +1108,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="26" t="inlineStr">
         <is>
-          <t>Modelo lógico en tercera forma normal para PostgreSQL, con moderación, auditoría y trazabilidad SCD Tipo 2.</t>
+          <t>Modelo lógico en tercera forma normal para PostgreSQL, con verificación de prestadores, moderación, auditoría y trazabilidad SCD Tipo 2.</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1124,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="70" t="inlineStr">
         <is>
-          <t>21 entidades · 45 valores de dominio · PostgreSQL</t>
+          <t>23 entidades · 60 valores de dominio · PostgreSQL</t>
         </is>
       </c>
       <c r="B7" s="71" t="n"/>
@@ -1144,7 +1146,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="76" t="inlineStr">
         <is>
-          <t>El modelo organiza las cuentas, perfiles de prestadores, servicios publicados, solicitudes, mensajería y calificaciones de Moica. El módulo de Moderación y Auditoría incorpora casos de investigación, un catálogo de medidas administrativas y un historial temporal SCD2 que permite reconstruir apelaciones, reversiones y reaperturas sin perder decisiones anteriores.</t>
+          <t>El modelo organiza las cuentas, perfiles de prestadores, servicios publicados, solicitudes, mensajería y calificaciones de Moica. El bloque de Prestadores incorpora la verificación documental en dos niveles mediante solicitudes revisadas manualmente y un expediente de archivos privados del que solo se persisten la clave opaca de almacenamiento y sus metadatos. El módulo de Moderación y Auditoría incorpora casos de investigación, un catálogo de medidas administrativas y un historial temporal SCD2 que permite reconstruir apelaciones, reversiones y reaperturas sin perder decisiones anteriores.</t>
         </is>
       </c>
       <c r="B11" s="71" t="n"/>
@@ -1249,18 +1251,18 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>PerfilPrestador, MedioContactoPrestador, TrabajoPortafolio, ImagenTrabajoPortafolio</t>
+          <t>PerfilPrestador, MedioContactoPrestador, TrabajoPortafolio, ImagenTrabajoPortafolio, SolicitudVerificacionPrestador, DocumentoVerificacionPrestador</t>
         </is>
       </c>
       <c r="D18" s="77" t="n"/>
       <c r="E18" s="78" t="n"/>
       <c r="F18" s="42" t="inlineStr">
         <is>
-          <t>Presentación pública, contacto y portafolio del prestador.</t>
+          <t>Presentación pública, contacto, portafolio y verificación documental del prestador.</t>
         </is>
       </c>
       <c r="G18" s="78" t="n"/>
@@ -1472,7 +1474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1540,7 +1542,7 @@
         </is>
       </c>
       <c r="J4" s="8">
-        <f>COUNTA(A9:A18)</f>
+        <f>COUNTA(A9:A19)</f>
         <v/>
       </c>
     </row>
@@ -1551,7 +1553,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTA(A22:A26)</f>
+        <f>COUNTA(A23:A28)</f>
         <v/>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -1560,7 +1562,7 @@
         </is>
       </c>
       <c r="E5" s="8">
-        <f>COUNTA(B30:B30)</f>
+        <f>COUNTA(B32:B33)</f>
         <v/>
       </c>
       <c r="G5" s="84" t="inlineStr">
@@ -2050,17 +2052,17 @@
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>fechaCreacion</t>
+          <t>nivelVerificacion</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Instante en que se creó el perfil de prestador.</t>
+          <t>Nivel de verificación documental vigente del perfil.</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>NivelVerificacionPrestador</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2075,367 +2077,483 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>SIN_VERIFICAR</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dominio NivelVerificacionPrestador</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Debe pertenecer al dominio definido. La aplicación lo actualiza al aprobar o revocar una solicitud de verificación; sin VERIFICADO_BASICO el perfil no es público.</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>BD + aplicación</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Derivado operativo</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>fechaCreacion</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Instante en que se creó el perfil de prestador.</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>fechaActualizacion</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Instante de la última modificación del perfil.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>La aplicación actualiza este valor cada vez que modifica el registro.</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Aplicación</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Auditoría</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="65" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="65" t="inlineStr">
         <is>
           <t>Relaciones directas</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Relación</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Origen</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Cardinalidad</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>FK en destino</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>ON DELETE</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Significado</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>usuarioPerfilPrestador</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Usuario</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>PerfilPrestador</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>1 a 0..1</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>PerfilPrestador.idPrestador</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Un usuario puede crear como máximo un perfil de prestador.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>municipioPerfilPrestador</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>PerfilPrestador</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>1 a 0..N</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>PerfilPrestador.idMunicipioPrincipal</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Cada perfil selecciona un municipio principal.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>perfilPrestadorMedioContacto</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>PerfilPrestador</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>MedioContactoPrestador</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>1 a 0..N</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>MedioContactoPrestador.idPrestador</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Un prestador puede publicar varios medios de contacto.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>perfilPrestadorTrabajoPortafolio</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>PerfilPrestador</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>TrabajoPortafolio</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>1 a 0..N</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>TrabajoPortafolio.idPrestador</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Un prestador puede mostrar varios trabajos.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>perfilPrestadorSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>PerfilPrestador</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.idPrestador</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Un prestador puede presentar varias solicitudes de verificación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>perfilPrestadorServicioPublicado</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>PerfilPrestador</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>ServicioPublicado</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>1 a 0..N</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>ServicioPublicado.idPrestador</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Un prestador puede publicar varios servicios.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="65" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="65" t="inlineStr">
         <is>
           <t>Restricciones implementadas en la base de datos</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Columnas</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Regla</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Capa</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="32" ht="38" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>pkPerfilPrestador</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>idPrestador</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Identificador único y compartido con Usuario.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>ckPerfilPrestadorNivelVerificacion</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>nivelVerificacion</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Debe pertenecer al dominio NivelVerificacionPrestador.</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Base de datos</t>
         </is>
@@ -2445,9 +2563,9 @@
   <mergeCells count="8">
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A30:J30"/>
     <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A20:J20"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="B4:C4"/>
@@ -4453,6 +4571,1903 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Intento registrado de un perfil de prestador para obtener o renovar un nivel de verificación documental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Prestadores</t>
+        </is>
+      </c>
+      <c r="C4" s="83" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Naturaleza</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Entidad transaccional</t>
+        </is>
+      </c>
+      <c r="F4" s="83" t="n"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Clave primaria</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>idSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Atributos</t>
+        </is>
+      </c>
+      <c r="J4" s="8">
+        <f>COUNTA(A9:A18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <f>COUNTA(A22:A24)</f>
+        <v/>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Restricciones BD</t>
+        </is>
+      </c>
+      <c r="E5" s="8">
+        <f>COUNTA(B28:B33)</f>
+        <v/>
+      </c>
+      <c r="G5" s="84" t="inlineStr">
+        <is>
+          <t>La revisión es manual: el nivel previo, las transiciones y el segundo factor del revisor se validan en la aplicación.</t>
+        </is>
+      </c>
+      <c r="H5" s="85" t="n"/>
+      <c r="I5" s="85" t="n"/>
+      <c r="J5" s="83" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="65" t="inlineStr">
+        <is>
+          <t>Atributos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Tipo PostgreSQL</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Clave</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Predeterminado</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Dominio o referencia</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Regla o validación</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>idSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Identificador técnico de la solicitud de verificación.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Valor único y positivo.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>idPrestador</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Perfil de prestador que solicita la verificación.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>PerfilPrestador.idPrestador</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>idAdministradorRevisor</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Administrador que tomó la solicitud y la resolvió.</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Administrador.idAdministrador</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Debe existir cuando la solicitud deja de estar PENDIENTE; la sesión debe haber verificado el segundo factor.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Aplicación</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>nivelSolicitado</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Nivel de verificación que se pretende obtener.</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>NivelVerificacionSolicitado</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Dominio NivelVerificacionSolicitado</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Debe pertenecer al dominio definido. El nivel PROFESIONAL exige una verificación básica vigente, comprobada en la aplicación.</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>BD + aplicación</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>estadoSolicitud</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estado vigente de la solicitud de verificación.</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>EstadoSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Dominio EstadoSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Debe pertenecer al dominio definido; las transiciones permitidas se validan en la aplicación.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>BD + aplicación</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Derivado operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>observacionResolucion</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Observación o motivo que el administrador registra al resolver.</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Obligatoria y no vacía cuando el estado es RECHAZADA o REVOCADA.</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>fechaSolicitud</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Instante en que el prestador envió el expediente.</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>fechaInicioRevision</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Instante en que un administrador tomó la solicitud.</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>No puede ser anterior a fechaSolicitud.</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>fechaResolucion</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Instante en que la solicitud fue aprobada, rechazada o revocada.</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Obligatoria en los estados finales y nunca anterior a fechaSolicitud.</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>fechaActualizacion</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Instante de la última modificación de la solicitud.</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>La aplicación actualiza este valor cada vez que modifica el registro.</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Aplicación</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>Relaciones directas</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Origen</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Cardinalidad</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>FK en destino</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>ON DELETE</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Significado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>perfilPrestadorSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>PerfilPrestador</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.idPrestador</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Un prestador puede presentar varias solicitudes de verificación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>administradorSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>1 a 0..N; solicitud 0..1</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.idAdministradorRevisor</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Cada solicitud conserva el administrador que la revisó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>solicitudVerificacionDocumento</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador.idSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Cada solicitud agrupa los documentos privados de su expediente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="65" t="inlineStr">
+        <is>
+          <t>Restricciones implementadas en la base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Columnas</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Capa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>pkSolicitudVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>idSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Identificador único de la solicitud de verificación.</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>uqSolicitudVerificacionAbierta</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>idPrestador, nivelSolicitado</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Índice único parcial WHERE estadoSolicitud IN ('PENDIENTE', 'EN_REVISION'): una sola solicitud abierta por nivel y perfil.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>ckSolicitudVerificacionNivel</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>nivelSolicitado</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Debe pertenecer al dominio NivelVerificacionSolicitado.</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>ckSolicitudVerificacionEstado</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>estadoSolicitud</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Debe pertenecer al dominio EstadoSolicitudVerificacion.</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>ckSolicitudVerificacionObservacion</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>estadoSolicitud, observacionResolucion</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Los estados RECHAZADA y REVOCADA exigen una observación no vacía.</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>ckSolicitudVerificacionFechas</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>fechaSolicitud, fechaInicioRevision, fechaResolucion</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>fechaInicioRevision y fechaResolucion no pueden ser anteriores a fechaSolicitud, y los estados finales exigen fechaResolucion.</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Archivo privado que forma parte del expediente documental de una solicitud de verificación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Prestadores</t>
+        </is>
+      </c>
+      <c r="C4" s="83" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Naturaleza</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Entidad dependiente</t>
+        </is>
+      </c>
+      <c r="F4" s="83" t="n"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Clave primaria</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>idDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Atributos</t>
+        </is>
+      </c>
+      <c r="J4" s="8">
+        <f>COUNTA(A9:A16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <f>COUNTA(A20:A20)</f>
+        <v/>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Restricciones BD</t>
+        </is>
+      </c>
+      <c r="E5" s="8">
+        <f>COUNTA(B24:B28)</f>
+        <v/>
+      </c>
+      <c r="G5" s="84" t="inlineStr">
+        <is>
+          <t>La base de datos guarda una clave opaca y metadatos; el binario reside en un almacenamiento privado con acceso temporal autorizado.</t>
+        </is>
+      </c>
+      <c r="H5" s="85" t="n"/>
+      <c r="I5" s="85" t="n"/>
+      <c r="J5" s="83" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="65" t="inlineStr">
+        <is>
+          <t>Atributos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Tipo PostgreSQL</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Clave</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Predeterminado</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Dominio o referencia</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Regla o validación</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>idDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Identificador técnico del documento del expediente.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Valor único y positivo.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>idSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Solicitud de verificación a la que pertenece el documento.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.idSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>tipoDocumento</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Clase de respaldo presentado dentro del expediente.</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>TipoDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Dominio TipoDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Debe pertenecer al dominio definido.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>claveAlmacenamiento</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Clave opaca con la que el servicio de almacenamiento privado localiza el archivo.</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(300)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>No es una dirección pública ni permanente y nunca se expone en respuestas públicas.</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>BD + aplicación</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>nombreOriginal</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Nombre saneado del archivo tal como lo cargó el prestador.</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>varchar(255)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>La aplicación sanea el nombre antes de almacenarlo.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Aplicación</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>tipoMime</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Tipo MIME validado del archivo cargado.</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Solo se admiten image/jpeg, image/png y application/pdf.</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>tamanoBytes</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Tamaño del archivo expresado en bytes.</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Mayor que cero y no superior al máximo de 5 MB; el límite operativo es configurable por debajo de ese tope.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>BD + aplicación</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>fechaCarga</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Instante en que se cargó el documento.</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>Relaciones directas</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Origen</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Cardinalidad</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>FK en destino</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>ON DELETE</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Significado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>solicitudVerificacionDocumento</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador.idSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Cada solicitud agrupa los documentos privados de su expediente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="65" t="inlineStr">
+        <is>
+          <t>Restricciones implementadas en la base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Columnas</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Capa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>pkDocumentoVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>idDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Identificador único del documento del expediente.</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>uqDocumentoVerificacionClave</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>claveAlmacenamiento</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>La clave de almacenamiento identifica un único archivo privado.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>ckDocumentoVerificacionTipo</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>tipoDocumento</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Debe pertenecer al dominio TipoDocumentoVerificacion.</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>ckDocumentoVerificacionMime</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>tipoMime</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>tipoMime IN ('image/jpeg', 'image/png', 'application/pdf').</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>ckDocumentoVerificacionTamano</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>tamanoBytes</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>tamanoBytes &gt; 0 AND tamanoBytes &lt;= 5242880.</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
@@ -4947,1528 +6962,6 @@
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A13:J13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
-        <is>
-          <t>SubcategoriaServicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="48" t="inlineStr">
-        <is>
-          <t>Clasificación específica perteneciente a una categoría y utilizada para clasificar servicios publicados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Bloque</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="C4" s="83" t="n"/>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Naturaleza</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Catálogo</t>
-        </is>
-      </c>
-      <c r="F4" s="83" t="n"/>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Clave primaria</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>idSubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Atributos</t>
-        </is>
-      </c>
-      <c r="J4" s="8">
-        <f>COUNTA(A9:A12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Relaciones</t>
-        </is>
-      </c>
-      <c r="B5" s="8">
-        <f>COUNTA(A16:A17)</f>
-        <v/>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Restricciones BD</t>
-        </is>
-      </c>
-      <c r="E5" s="8">
-        <f>COUNTA(B21:B22)</f>
-        <v/>
-      </c>
-      <c r="G5" s="84" t="inlineStr">
-        <is>
-          <t>Las reglas de flujo y coherencia entre participantes se validan en la aplicación.</t>
-        </is>
-      </c>
-      <c r="H5" s="85" t="n"/>
-      <c r="I5" s="85" t="n"/>
-      <c r="J5" s="83" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="66" t="inlineStr">
-        <is>
-          <t>Atributos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Atributo</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Tipo PostgreSQL</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Clave</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Nulo</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>Predeterminado</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>Dominio o referencia</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Regla o validación</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Naturaleza</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>idSubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Identificador técnico de la subcategoría.</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Valor único y positivo.</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Técnico</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>idCategoriaServicio</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Categoría general a la que pertenece la subcategoría.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>smallint</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>CategoriaServicio.idCategoriaServicio</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Nombre de la subcategoría.</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>varchar(100)</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>UQ compuesta</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>No se repite dentro de la misma categoría.</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>descripcion</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Explicación opcional del alcance de la subcategoría.</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="66" t="inlineStr">
-        <is>
-          <t>Relaciones directas</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Relación</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Origen</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Destino</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Cardinalidad</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>FK en destino</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>ON DELETE</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Significado</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>categoriaServicioSubcategoria</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>CategoriaServicio</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>SubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>1 a 0..N</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>SubcategoriaServicio.idCategoriaServicio</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Una categoría agrupa subcategorías.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>subcategoriaServicioServicioPublicado</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>SubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>ServicioPublicado</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>1 a 0..N</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>ServicioPublicado.idSubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Cada servicio pertenece a una subcategoría.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="66" t="inlineStr">
-        <is>
-          <t>Restricciones implementadas en la base de datos</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Columnas</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Regla</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Capa</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>pkSubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>idSubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Identificador único de la subcategoría.</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>uqSubcategoriaServicioCategoriaNombre</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>idCategoriaServicio, nombre</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>No repite una subcategoría dentro de la misma categoría.</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A19:J19"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
-        <is>
-          <t>ServicioPublicado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="48" t="inlineStr">
-        <is>
-          <t>Oferta concreta que un prestador publica para que los clientes puedan encontrarla y solicitarla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Bloque</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="C4" s="83" t="n"/>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Naturaleza</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Entidad principal</t>
-        </is>
-      </c>
-      <c r="F4" s="83" t="n"/>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Clave primaria</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>idServicioPublicado</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Atributos</t>
-        </is>
-      </c>
-      <c r="J4" s="8">
-        <f>COUNTA(A9:A17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Relaciones</t>
-        </is>
-      </c>
-      <c r="B5" s="8">
-        <f>COUNTA(A21:A24)</f>
-        <v/>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Restricciones BD</t>
-        </is>
-      </c>
-      <c r="E5" s="8">
-        <f>COUNTA(B28:B29)</f>
-        <v/>
-      </c>
-      <c r="G5" s="84" t="inlineStr">
-        <is>
-          <t>Las reglas de flujo y coherencia entre participantes se validan en la aplicación.</t>
-        </is>
-      </c>
-      <c r="H5" s="85" t="n"/>
-      <c r="I5" s="85" t="n"/>
-      <c r="J5" s="83" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="66" t="inlineStr">
-        <is>
-          <t>Atributos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Atributo</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Tipo PostgreSQL</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Clave</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Nulo</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>Predeterminado</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>Dominio o referencia</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Regla o validación</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Naturaleza</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>idServicioPublicado</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Identificador técnico del servicio publicado.</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Valor único y positivo.</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Técnico</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>idPrestador</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Prestador que ofrece el servicio.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>PerfilPrestador.idPrestador</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>idSubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Subcategoría en la que se clasifica el servicio.</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>SubcategoriaServicio.idSubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Nombre público del servicio.</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>varchar(150)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>descripcion</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Explicación del servicio ofrecido.</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>precioReferencia</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Precio orientativo del servicio; si es nulo, se mostrará «A convenir».</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>numeric(12,2)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Si existe, debe ser mayor que cero.</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>BD + aplicación</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>estado</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Indica si el servicio puede mostrarse y recibir solicitudes.</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>EstadoServicio</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Dominio EstadoServicio</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Debe pertenecer al dominio definido.</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>fechaCreacion</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Instante en que se publicó el servicio.</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>fechaActualizacion</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Instante de la última modificación del servicio.</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>La aplicación actualiza este valor cada vez que modifica el registro.</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Aplicación</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="66" t="inlineStr">
-        <is>
-          <t>Relaciones directas</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Relación</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Origen</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Destino</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Cardinalidad</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>FK en destino</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>ON DELETE</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Significado</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>subcategoriaServicioServicioPublicado</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>SubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>ServicioPublicado</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>1 a 0..N</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ServicioPublicado.idSubcategoriaServicio</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Cada servicio pertenece a una subcategoría.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>perfilPrestadorServicioPublicado</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>PerfilPrestador</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>ServicioPublicado</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>1 a 0..N</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>ServicioPublicado.idPrestador</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Un prestador puede publicar varios servicios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>servicioPublicadoImagenServicio</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>ServicioPublicado</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>ImagenServicioPublicado</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>1 a 0..N</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>ImagenServicioPublicado.idServicioPublicado</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Un servicio puede mostrar varias imágenes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>servicioPublicadoSolicitudServicio</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>ServicioPublicado</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>SolicitudServicio</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>1 a 0..N</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>SolicitudServicio.idServicioPublicado</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Un servicio puede recibir varias solicitudes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="66" t="inlineStr">
-        <is>
-          <t>Restricciones implementadas en la base de datos</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Columnas</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Regla</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Capa</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>pkServicioPublicado</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>idServicioPublicado</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Identificador único del servicio.</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>ckServicioPublicadoPrecio</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>precioReferencia</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>precioReferencia IS NULL OR precioReferencia &gt; 0.</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A19:J19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6498,6 +6991,1528 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="47" t="inlineStr">
         <is>
+          <t>SubcategoriaServicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Clasificación específica perteneciente a una categoría y utilizada para clasificar servicios publicados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="C4" s="83" t="n"/>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Naturaleza</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="F4" s="83" t="n"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Clave primaria</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>idSubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>Atributos</t>
+        </is>
+      </c>
+      <c r="J4" s="8">
+        <f>COUNTA(A9:A12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <f>COUNTA(A16:A17)</f>
+        <v/>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Restricciones BD</t>
+        </is>
+      </c>
+      <c r="E5" s="8">
+        <f>COUNTA(B21:B22)</f>
+        <v/>
+      </c>
+      <c r="G5" s="84" t="inlineStr">
+        <is>
+          <t>Las reglas de flujo y coherencia entre participantes se validan en la aplicación.</t>
+        </is>
+      </c>
+      <c r="H5" s="85" t="n"/>
+      <c r="I5" s="85" t="n"/>
+      <c r="J5" s="83" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="66" t="inlineStr">
+        <is>
+          <t>Atributos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Tipo PostgreSQL</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Clave</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Predeterminado</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Dominio o referencia</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Regla o validación</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>idSubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Identificador técnico de la subcategoría.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Valor único y positivo.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>idCategoriaServicio</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Categoría general a la que pertenece la subcategoría.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CategoriaServicio.idCategoriaServicio</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Nombre de la subcategoría.</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>UQ compuesta</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>No se repite dentro de la misma categoría.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Explicación opcional del alcance de la subcategoría.</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="66" t="inlineStr">
+        <is>
+          <t>Relaciones directas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Origen</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Cardinalidad</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>FK en destino</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>ON DELETE</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Significado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>categoriaServicioSubcategoria</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>CategoriaServicio</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>SubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>SubcategoriaServicio.idCategoriaServicio</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Una categoría agrupa subcategorías.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>subcategoriaServicioServicioPublicado</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>SubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ServicioPublicado</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>ServicioPublicado.idSubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Cada servicio pertenece a una subcategoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="66" t="inlineStr">
+        <is>
+          <t>Restricciones implementadas en la base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Columnas</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Capa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>pkSubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>idSubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Identificador único de la subcategoría.</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>uqSubcategoriaServicioCategoriaNombre</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>idCategoriaServicio, nombre</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>No repite una subcategoría dentro de la misma categoría.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A19:J19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>ServicioPublicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Oferta concreta que un prestador publica para que los clientes puedan encontrarla y solicitarla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="C4" s="83" t="n"/>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Naturaleza</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Entidad principal</t>
+        </is>
+      </c>
+      <c r="F4" s="83" t="n"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Clave primaria</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>idServicioPublicado</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>Atributos</t>
+        </is>
+      </c>
+      <c r="J4" s="8">
+        <f>COUNTA(A9:A17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <f>COUNTA(A21:A24)</f>
+        <v/>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Restricciones BD</t>
+        </is>
+      </c>
+      <c r="E5" s="8">
+        <f>COUNTA(B28:B29)</f>
+        <v/>
+      </c>
+      <c r="G5" s="84" t="inlineStr">
+        <is>
+          <t>Las reglas de flujo y coherencia entre participantes se validan en la aplicación.</t>
+        </is>
+      </c>
+      <c r="H5" s="85" t="n"/>
+      <c r="I5" s="85" t="n"/>
+      <c r="J5" s="83" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="66" t="inlineStr">
+        <is>
+          <t>Atributos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Tipo PostgreSQL</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Clave</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Predeterminado</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Dominio o referencia</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Regla o validación</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>idServicioPublicado</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Identificador técnico del servicio publicado.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Valor único y positivo.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>idPrestador</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Prestador que ofrece el servicio.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>PerfilPrestador.idPrestador</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>idSubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Subcategoría en la que se clasifica el servicio.</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>SubcategoriaServicio.idSubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Nombre público del servicio.</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>varchar(150)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Explicación del servicio ofrecido.</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>precioReferencia</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Precio orientativo del servicio; si es nulo, se mostrará «A convenir».</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>numeric(12,2)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Si existe, debe ser mayor que cero.</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>BD + aplicación</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Indica si el servicio puede mostrarse y recibir solicitudes.</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>EstadoServicio</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Dominio EstadoServicio</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Debe pertenecer al dominio definido.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>fechaCreacion</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Instante en que se publicó el servicio.</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>fechaActualizacion</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Instante de la última modificación del servicio.</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>La aplicación actualiza este valor cada vez que modifica el registro.</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Aplicación</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="66" t="inlineStr">
+        <is>
+          <t>Relaciones directas</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Origen</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Cardinalidad</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>FK en destino</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>ON DELETE</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Significado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>subcategoriaServicioServicioPublicado</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>ServicioPublicado</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>ServicioPublicado.idSubcategoriaServicio</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Cada servicio pertenece a una subcategoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>perfilPrestadorServicioPublicado</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>PerfilPrestador</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ServicioPublicado</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>ServicioPublicado.idPrestador</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Un prestador puede publicar varios servicios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>servicioPublicadoImagenServicio</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>ServicioPublicado</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>ImagenServicioPublicado</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>ImagenServicioPublicado.idServicioPublicado</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Un servicio puede mostrar varias imágenes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>servicioPublicadoSolicitudServicio</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>ServicioPublicado</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>SolicitudServicio</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>1 a 0..N</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>SolicitudServicio.idServicioPublicado</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Un servicio puede recibir varias solicitudes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="66" t="inlineStr">
+        <is>
+          <t>Restricciones implementadas en la base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Columnas</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Capa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>pkServicioPublicado</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>idServicioPublicado</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Identificador único del servicio.</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>ckServicioPublicadoPrecio</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>precioReferencia</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>precioReferencia IS NULL OR precioReferencia &gt; 0.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A19:J19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
           <t>ImagenServicioPublicado</t>
         </is>
       </c>
@@ -7108,7 +9123,335 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>Criterios de diseño del modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Definiciones vigentes para la verificación de prestadores, la moderación, la auditoría y la trazabilidad SCD Tipo 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>Criterios vigentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>N.º</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Elemento</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Definición</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Función en el modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CasoModeracion</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Representa el expediente de investigación asociado con una conducta reportada.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Concentra participantes, responsable, estado, resultado, resolución y medida vigentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MedidaAdministrativa</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Es el catálogo de sanciones y acciones administrativas preestablecidas.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Las medidas se referencian mediante claves foráneas y conservan códigos estables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>HistorialCaso</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Implementa la trazabilidad mediante SCD Tipo 2.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Cada evento genera una versión completa con inicio, fin y marca de vigencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Usuario.estadoCuenta</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Funciona como proyección operativa del estado vigente.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>La evidencia histórica de los cambios administrativos reside en HistorialCaso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Estado y resultado del caso</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Se representan mediante dominios separados.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>EstadoCasoModeracion expresa el flujo; ResultadoCasoModeracion expresa la decisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Apelaciones y reversiones</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Generan una nueva versión sin sobrescribir la evidencia histórica.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Se cierra la vigencia actual y se inserta la fotografía completa del estado resultante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Reapertura del caso</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Se gestiona dentro del mismo CasoModeracion.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>El caso pasa a REABIERTO y conserva sus resoluciones históricas en versiones cerradas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Consistencia transaccional</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>La proyección vigente y la versión SCD2 se actualizan de forma conjunta.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>El cierre de la vigencia y la inserción de la nueva versión ocurren en una sola transacción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Registra cada intento de obtener o renovar un nivel de verificación.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Conserva nivel solicitado, estado, revisor, observación y fechas de todo el ciclo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Representa cada archivo privado del expediente documental.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Persiste una clave opaca de almacenamiento y metadatos; el binario nunca se guarda en PostgreSQL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>PerfilPrestador.nivelVerificacion</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Funciona como proyección operativa del nivel vigente.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>La evidencia de cómo se alcanzó reside en las solicitudes de verificación del perfil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Verificación y segundo factor</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Son mecanismos separados y no se sustituyen entre sí.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>El TOTP protege el inicio de sesión; la verificación documental respalda la identidad del perfil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Resolución de verificaciones</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Es siempre manual y responsabilidad de una persona administradora.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Las reglas que dependen de otras filas o del estado de la sesión se validan en la aplicación.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8172,7 +10515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8922,235 +11265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
-        <is>
-          <t>Criterios de diseño del modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="48" t="inlineStr">
-        <is>
-          <t>Definiciones vigentes para la moderación, la auditoría y la trazabilidad SCD Tipo 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
-        <is>
-          <t>Criterios vigentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>N.º</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Elemento</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Definición</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Función en el modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>CasoModeracion</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Representa el expediente de investigación asociado con una conducta reportada.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Concentra participantes, responsable, estado, resultado, resolución y medida vigentes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>MedidaAdministrativa</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Es el catálogo de sanciones y acciones administrativas preestablecidas.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Las medidas se referencian mediante claves foráneas y conservan códigos estables.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>HistorialCaso</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Implementa la trazabilidad mediante SCD Tipo 2.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Cada evento genera una versión completa con inicio, fin y marca de vigencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Usuario.estadoCuenta</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Funciona como proyección operativa del estado vigente.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>La evidencia histórica de los cambios administrativos reside en HistorialCaso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estado y resultado del caso</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Se representan mediante dominios separados.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>EstadoCasoModeracion expresa el flujo; ResultadoCasoModeracion expresa la decisión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Apelaciones y reversiones</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Generan una nueva versión sin sobrescribir la evidencia histórica.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Se cierra la vigencia actual y se inserta la fotografía completa del estado resultante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Reapertura del caso</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Se gestiona dentro del mismo CasoModeracion.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>El caso pasa a REABIERTO y conserva sus resoluciones históricas en versiones cerradas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Consistencia transaccional</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>La proyección vigente y la versión SCD2 se actualizan de forma conjunta.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>El cierre de la vigencia y la inserción de la nueva versión ocurren en una sola transacción.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9769,7 +11884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10689,7 +12804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12181,7 +14296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13117,7 +15232,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14847,7 +16962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15892,6 +18007,336 @@
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>HistorialCaso.tipoEvento</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>NivelVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>SIN_VERIFICAR</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>El perfil no ha superado la verificación documental; no aparece públicamente ni admite servicios activos.</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>PerfilPrestador.nivelVerificacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>NivelVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>VERIFICADO_BASICO</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Una persona administradora aprobó la documentación oficial de identidad del responsable del perfil.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>PerfilPrestador.nivelVerificacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>NivelVerificacionPrestador</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>PROFESIONAL_VERIFICADO</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Sobre la verificación básica, una persona administradora aprobó documentación profesional, técnica o comercial.</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>PerfilPrestador.nivelVerificacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>NivelVerificacionSolicitado</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>BASICA</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>La solicitud pretende obtener la verificación básica de identidad.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.nivelSolicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>NivelVerificacionSolicitado</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>PROFESIONAL</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>La solicitud pretende obtener la verificación profesional; exige una básica vigente.</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.nivelSolicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>EstadoSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>El expediente fue enviado y espera que un administrador lo tome.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.estadoSolicitud</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>EstadoSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>EN_REVISION</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Un administrador tomó la solicitud y analiza los documentos presentados.</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.estadoSolicitud</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>EstadoSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>La documentación fue aceptada y el perfil alcanzó el nivel solicitado.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.estadoSolicitud</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>EstadoSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>La documentación no fue aceptada; exige una observación y el perfil conserva su nivel anterior.</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.estadoSolicitud</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>EstadoSolicitudVerificacion</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>REVOCADA</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Una verificación previamente aprobada quedó sin efecto; exige una observación.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>SolicitudVerificacionPrestador.estadoSolicitud</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>TipoDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>IDENTIDAD</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Documento oficial de identidad de la persona responsable del perfil.</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador.tipoDocumento</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>TipoDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>CERTIFICACION</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Certificado técnico o profesional que respalda la actividad declarada.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador.tipoDocumento</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>TipoDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>CONSTANCIA</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Constancia de experiencia, laboral o de trabajos realizados.</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador.tipoDocumento</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>TipoDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO_NEGOCIO</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Documento comercial o registro del emprendimiento o la PYME.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador.tipoDocumento</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>TipoDocumentoVerificacion</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>OTRO_RESPALDO</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Cualquier otro respaldo aportado por el prestador y valorado por la persona revisora.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>DocumentoVerificacionPrestador.tipoDocumento</t>
         </is>
       </c>
     </row>
@@ -17210,7 +19655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -17235,7 +19680,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="53" t="inlineStr">
         <is>
-          <t>Extensión de Usuario con permisos para gestionar casos de moderación, revisar apelaciones y aplicar o revertir medidas administrativas.</t>
+          <t>Extensión de Usuario con permisos para resolver verificaciones de prestadores, gestionar casos de moderación, revisar apelaciones y aplicar o revertir medidas administrativas.</t>
         </is>
       </c>
     </row>
@@ -17296,7 +19741,7 @@
         </is>
       </c>
       <c r="B5" s="54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="78" t="n"/>
       <c r="D5" s="15" t="inlineStr">
@@ -17594,7 +20039,7 @@
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>administradorCasoModeracion</t>
+          <t>administradorSolicitudVerificacion</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -17604,17 +20049,17 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>CasoModeracion</t>
+          <t>SolicitudVerificacionPrestador</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>1 a 0..N; caso 0..1</t>
+          <t>1 a 0..N; solicitud 0..1</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>CasoModeracion.idAdministradorResponsable</t>
+          <t>SolicitudVerificacionPrestador.idAdministradorRevisor</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -17624,7 +20069,7 @@
       </c>
       <c r="G15" s="18" t="inlineStr">
         <is>
-          <t>Un caso puede asignarse a un administrador responsable.</t>
+          <t>Cada solicitud de verificación conserva el administrador que la revisó.</t>
         </is>
       </c>
       <c r="H15" s="14" t="n"/>
@@ -17634,7 +20079,7 @@
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>administradorHistorialCaso</t>
+          <t>administradorCasoModeracion</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
@@ -17644,17 +20089,17 @@
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>HistorialCaso</t>
+          <t>CasoModeracion</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>1 a 0..N; versión 0..1</t>
+          <t>1 a 0..N; caso 0..1</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>HistorialCaso.idAdministradorResponsable</t>
+          <t>CasoModeracion.idAdministradorResponsable</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -17664,88 +20109,96 @@
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>Cada versión puede conservar el administrador responsable vigente en ese momento.</t>
+          <t>Un caso puede asignarse a un administrador responsable.</t>
         </is>
       </c>
       <c r="H16" s="14" t="n"/>
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="14" t="n"/>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="14" t="n"/>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>administradorHistorialCaso</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>HistorialCaso</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>1 a 0..N; versión 0..1</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>HistorialCaso.idAdministradorResponsable</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Cada versión puede conservar el administrador responsable vigente en ese momento.</t>
+        </is>
+      </c>
       <c r="H17" s="14" t="n"/>
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="14" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>Restricciones implementadas en la base de datos</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Columnas</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>Regla</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Capa</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="14" t="n"/>
-      <c r="I19" s="14" t="n"/>
-      <c r="J19" s="14" t="n"/>
-    </row>
-    <row r="20" ht="46" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>pkAdministrador</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>idAdministrador</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>Identificador único y compartido con Usuario.</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
         </is>
       </c>
       <c r="F20" s="14" t="n"/>
@@ -17754,12 +20207,43 @@
       <c r="I20" s="14" t="n"/>
       <c r="J20" s="14" t="n"/>
     </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>pkAdministrador</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>idAdministrador</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>Identificador único y compartido con Usuario.</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A18:J18"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A7:J7"/>
@@ -17767,6 +20251,7 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A19:J19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/Dev/Moica - Diccionario de Datos.xlsx
+++ b/Docs/Dev/Moica - Diccionario de Datos.xlsx
@@ -2505,7 +2505,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="38" customHeight="1">
+    <row r="32" ht="46" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>PK</t>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1">
+    <row r="33" ht="46" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CK</t>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="38" customHeight="1">
+    <row r="28" ht="46" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>PK</t>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="38" customHeight="1">
+    <row r="29" ht="46" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>UQ</t>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Índice único parcial WHERE estadoSolicitud IN ('PENDIENTE', 'EN_REVISION'): una sola solicitud abierta por nivel y perfil.</t>
+          <t>Índice parcial: una solicitud abierta por perfil y nivel.</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -5493,7 +5493,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1">
+    <row r="30" ht="46" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>CK</t>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="38" customHeight="1">
+    <row r="31" ht="46" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t>CK</t>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="38" customHeight="1">
+    <row r="32" ht="46" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t>CK</t>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Los estados RECHAZADA y REVOCADA exigen una observación no vacía.</t>
+          <t>RECHAZADA y REVOCADA exigen una observación no vacía.</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1">
+    <row r="33" ht="46" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CK</t>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>fechaInicioRevision y fechaResolucion no pueden ser anteriores a fechaSolicitud, y los estados finales exigen fechaResolucion.</t>
+          <t>Revisión y resolución nunca preceden a fechaSolicitud.</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -5606,8 +5606,8 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="B4:C4"/>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="38" customHeight="1">
+    <row r="24" ht="46" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>PK</t>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="38" customHeight="1">
+    <row r="25" ht="46" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t>UQ</t>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>La clave de almacenamiento identifica un único archivo privado.</t>
+          <t>La clave de almacenamiento identifica un único archivo.</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -6366,7 +6366,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="38" customHeight="1">
+    <row r="26" ht="46" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t>CK</t>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="38" customHeight="1">
+    <row r="27" ht="46" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>CK</t>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>tipoMime IN ('image/jpeg', 'image/png', 'application/pdf').</t>
+          <t>Solo image/jpeg, image/png y application/pdf.</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -6420,7 +6420,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="38" customHeight="1">
+    <row r="28" ht="46" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
           <t>CK</t>
